--- a/config/talent_tree.xlsx
+++ b/config/talent_tree.xlsx
@@ -1254,14 +1254,14 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>基礎</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>基礎</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Base</t>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　対象：仲間の基礎ステータス</t>
+          <t>对象：伙伴的基础状态</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>昇格</t>
+          <t>升级</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>対象：仲間のステータス初期値</t>
+          <t>对象：伙伴状态初始值</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>対象属性の仲間のみ有効#F36##C0xf76b45#(第一属性)</t>
+          <t>对象属性的伙伴有效#F36##C0xf76b45#（第一属性）</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>対象コンテンツでのみ有効</t>
+          <t>仅适用于目标内容</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
